--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48212,6 +48212,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G2081" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48235,6 +48235,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G2082" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48258,6 +48258,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G2083" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G2084" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48122,22 +48122,22 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2077" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="C2077" t="n">
-        <v>1.24000000953674</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D2077" t="n">
-        <v>1.22000002861023</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.22000002861023</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.24000000953674</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="G2077" t="s">
         <v>7</v>
@@ -48145,22 +48145,22 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2078" t="n">
-        <v>3500</v>
+        <v>6500</v>
       </c>
       <c r="C2078" t="n">
-        <v>1.26999998092651</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="D2078" t="n">
-        <v>1.25</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.25</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.26999998092651</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="G2078" t="s">
         <v>7</v>
@@ -48168,22 +48168,22 @@
     </row>
     <row r="2079">
       <c r="A2079" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2079" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="C2079" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="D2079" t="n">
         <v>1.25</v>
-      </c>
-      <c r="D2079" t="n">
-        <v>1.22000002861023</v>
       </c>
       <c r="E2079" t="n">
         <v>1.25</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.22000002861023</v>
+        <v>1.26999998092651</v>
       </c>
       <c r="G2079" t="s">
         <v>7</v>
@@ -48191,22 +48191,22 @@
     </row>
     <row r="2080">
       <c r="A2080" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2080" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="C2080" t="n">
-        <v>1.24000000953674</v>
+        <v>1.25</v>
       </c>
       <c r="D2080" t="n">
-        <v>1.24000000953674</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.24000000953674</v>
+        <v>1.25</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.24000000953674</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="G2080" t="s">
         <v>7</v>
@@ -48214,22 +48214,22 @@
     </row>
     <row r="2081">
       <c r="A2081" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2081" t="n">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="C2081" t="n">
         <v>1.24000000953674</v>
       </c>
       <c r="D2081" t="n">
-        <v>1.23000001907349</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="E2081" t="n">
         <v>1.24000000953674</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.23000001907349</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="G2081" t="s">
         <v>7</v>
@@ -48237,22 +48237,22 @@
     </row>
     <row r="2082">
       <c r="A2082" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2082" t="n">
-        <v>5500</v>
+        <v>13000</v>
       </c>
       <c r="C2082" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D2082" t="n">
         <v>1.23000001907349</v>
       </c>
-      <c r="D2082" t="n">
-        <v>1.20000004768372</v>
-      </c>
       <c r="E2082" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="F2082" t="n">
         <v>1.23000001907349</v>
-      </c>
-      <c r="F2082" t="n">
-        <v>1.20000004768372</v>
       </c>
       <c r="G2082" t="s">
         <v>7</v>
@@ -48260,19 +48260,19 @@
     </row>
     <row r="2083">
       <c r="A2083" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2083" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="C2083" t="n">
-        <v>1.20000004768372</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="D2083" t="n">
         <v>1.20000004768372</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.20000004768372</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="F2083" t="n">
         <v>1.20000004768372</v>
@@ -48283,22 +48283,22 @@
     </row>
     <row r="2084">
       <c r="A2084" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2084" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="C2084" t="n">
-        <v>1.24000000953674</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D2084" t="n">
-        <v>1.13999998569489</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="E2084" t="n">
         <v>1.20000004768372</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.1599999666214</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="G2084" t="s">
         <v>7</v>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -54637,6 +54637,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2088">
+      <c r="A2088" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="H2088" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -54645,7 +54645,7 @@
         <v>11000</v>
       </c>
       <c r="C2088" t="n">
-        <v>1.16999995708466</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D2088" t="n">
         <v>1.08000004291534</v>
@@ -54660,6 +54660,32 @@
         <v>1.20000004768372</v>
       </c>
       <c r="H2088" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H2089" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -54689,6 +54689,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2090">
+      <c r="A2090" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H2090" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -54715,6 +54715,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2091">
+      <c r="A2091" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H2091" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -54793,6 +54793,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2094">
+      <c r="A2094" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2094" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48580,6 +48580,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2097">
+      <c r="A2097" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="G2097" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="F2098"/>
+      <c r="G2098" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48611,7 +48611,7 @@
         <v>17000</v>
       </c>
       <c r="C2098" t="n">
-        <v>1.3400000333786</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="D2098" t="n">
         <v>1.22000002861023</v>
@@ -48619,8 +48619,31 @@
       <c r="E2098" t="n">
         <v>1.27999997138977</v>
       </c>
-      <c r="F2098"/>
+      <c r="F2098" t="n">
+        <v>1.35000002384186</v>
+      </c>
       <c r="G2098" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F2099"/>
+      <c r="G2099" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48642,8 +48642,31 @@
       <c r="E2099" t="n">
         <v>1.3400000333786</v>
       </c>
-      <c r="F2099"/>
+      <c r="F2099" t="n">
+        <v>1.29999995231628</v>
+      </c>
       <c r="G2099" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2100"/>
+      <c r="G2100" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48665,7 +48665,9 @@
       <c r="E2100" t="n">
         <v>1.29999995231628</v>
       </c>
-      <c r="F2100"/>
+      <c r="F2100" t="n">
+        <v>1.26999998092651</v>
+      </c>
       <c r="G2100" t="s">
         <v>7</v>
       </c>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -48695,6 +48695,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2102">
+      <c r="A2102" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2102" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -55079,6 +55079,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2105">
+      <c r="A2105" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="H2105" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -55105,6 +55105,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2106">
+      <c r="A2106" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="H2106" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -61452,6 +61452,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2107">
+      <c r="A2107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2107" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I2107" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -61481,6 +61481,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2108">
+      <c r="A2108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2108" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2109" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I2109" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -61539,6 +61539,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2110">
+      <c r="A2110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2110" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I2110" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -61568,6 +61568,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2111">
+      <c r="A2111" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2111" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2112" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>500</v>
+      </c>
+      <c r="I2112" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -61626,6 +61626,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2113">
+      <c r="A2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2113" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2113" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -61655,6 +61655,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2114">
+      <c r="A2114" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2114" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2115" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2115" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LON.MI.xlsx
+++ b/data/LON.MI.xlsx
@@ -61713,6 +61713,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2116">
+      <c r="A2116" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2116" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>500</v>
+      </c>
+      <c r="I2116" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
